--- a/rules/CORE-000580/positive/03/data/unit-test-coreid-CG0325-positive03.xlsx
+++ b/rules/CORE-000580/positive/03/data/unit-test-coreid-CG0325-positive03.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000580\positive\03\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{782870FF-7FA5-4638-8B61-927EDDC0C1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A4D649-B429-4571-96C2-3D25ED365C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31740" yWindow="480" windowWidth="23265" windowHeight="14505" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="45">
   <si>
     <t>Product</t>
   </si>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Z</t>
+  </si>
+  <si>
+    <t>E007</t>
+  </si>
+  <si>
+    <t>E008</t>
   </si>
 </sst>
 </file>
@@ -812,7 +818,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>41</v>
@@ -832,7 +838,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>42</v>
